--- a/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,3; 86,21</t>
+          <t>33,5; 86,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,6; 90,48</t>
+          <t>49,81; 90,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 67,9</t>
+          <t>7,59; 65,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,56; 92,32</t>
+          <t>54,32; 92,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,85; 80,31</t>
+          <t>42,07; 79,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,63; 86,1</t>
+          <t>42,3; 84,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,92; 86,82</t>
+          <t>36,42; 87,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,55; 98,11</t>
+          <t>63,79; 97,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,84; 77,13</t>
+          <t>48,05; 77,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53,21; 82,74</t>
+          <t>55,22; 84,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 70,79</t>
+          <t>30,32; 69,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,48; 94,49</t>
+          <t>67,34; 94,37</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,39; 95,94</t>
+          <t>70,41; 95,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,11; 73,54</t>
+          <t>43,81; 73,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,79; 71,67</t>
+          <t>34,66; 69,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,17; 97,08</t>
+          <t>69,95; 97,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,26; 77,78</t>
+          <t>46,6; 77,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,04; 64,94</t>
+          <t>36,77; 64,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,83; 75,88</t>
+          <t>40,36; 76,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,99; 78,49</t>
+          <t>46,08; 78,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,95; 81,2</t>
+          <t>60,43; 81,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,43; 64,66</t>
+          <t>45,52; 64,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,24; 69,29</t>
+          <t>44,63; 68,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,7; 85,17</t>
+          <t>61,18; 85,25</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 68,32</t>
+          <t>14,38; 67,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,19; 74,47</t>
+          <t>39,31; 73,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,97; 77,84</t>
+          <t>27,78; 79,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,82; 90,68</t>
+          <t>51,97; 91,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,41; 86,7</t>
+          <t>48,56; 86,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,58; 83,45</t>
+          <t>55,92; 83,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 74,87</t>
+          <t>18,95; 69,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,21; 88,03</t>
+          <t>48,88; 86,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,81; 74,16</t>
+          <t>42,81; 76,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,24; 75,7</t>
+          <t>52,78; 75,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,48; 68,18</t>
+          <t>32,49; 69,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,99; 84,18</t>
+          <t>59,02; 84,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,63; 77,45</t>
+          <t>42,18; 75,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,47; 86,7</t>
+          <t>55,25; 87,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,91; 93,76</t>
+          <t>49,2; 93,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,27; 81,59</t>
+          <t>38,23; 79,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,69; 85,25</t>
+          <t>55,7; 85,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,0; 78,12</t>
+          <t>42,54; 75,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,81; 77,79</t>
+          <t>27,64; 75,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,48; 74,67</t>
+          <t>40,9; 73,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,98; 78,66</t>
+          <t>54,65; 78,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,88; 76,53</t>
+          <t>54,35; 77,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47,27; 81,1</t>
+          <t>48,3; 81,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,62; 71,35</t>
+          <t>46,97; 72,19</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,32; 74,63</t>
+          <t>53,79; 76,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,68; 73,21</t>
+          <t>56,49; 73,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,92; 66,39</t>
+          <t>43,48; 67,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,67</t>
+          <t>65,19; 84,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,47; 75,05</t>
+          <t>58,46; 74,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,12; 70,26</t>
+          <t>52,57; 69,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,52; 68,46</t>
+          <t>44,39; 69,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,11; 79,0</t>
+          <t>58,95; 79,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,77</t>
+          <t>59,94; 73,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,92; 68,92</t>
+          <t>57,16; 69,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 63,67</t>
+          <t>48,02; 63,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,47; 79,49</t>
+          <t>65,01; 78,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10533</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9365</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>20423</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16496</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21527</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8956</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>29787</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3271; 8404</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7006; 12735</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>620; 5345</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6521; 11063</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6826; 12970</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6831; 13636</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3536; 8534</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>15266; 23400</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12488; 20174</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16684; 25445</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5420; 12469</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>24199; 33915</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13109</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16719</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18519</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17538</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15703</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16442</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30648</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22221</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>34961</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10580; 14402</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12182; 20362</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6791; 13680</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14941; 20738</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12902; 21531</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11309; 19987</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8090; 15421</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11950; 20364</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>25811; 34949</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>26658; 38051</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17688; 27247</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>28933; 40317</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10912</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10814</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10774</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17867</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15067</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13833</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28779</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9056</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>25880</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1131; 5295</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7564; 14150</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2503; 7130</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7540; 13206</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7462; 13289</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14144; 21013</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1718; 6320</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10246; 18227</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9947; 17683</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23505; 33405</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5873; 12545</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20934; 30069</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13394</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15384</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8191</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9427</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16290</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16175</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6912</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16592</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29684</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31559</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15103</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>26019</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9303; 16692</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11673; 18466</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5092; 9716</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5991; 12517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12374; 18925</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11214; 20012</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3491; 9596</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>11535; 20837</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24193; 34547</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>25812; 36925</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11098; 18620</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>20608; 31675</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>53548</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>68522</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>90659</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114287</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>55336</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>116648</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29434; 41587</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46455; 60424</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20490; 31947</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>41428; 53707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>47642; 60804</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>51812; 68059</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22837; 35626</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>58373; 79100</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>81647; 99940</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>103352; 125068</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>47336; 62952</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>105685; 128287</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,5; 86,07</t>
+          <t>33,55; 85,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,81; 90,54</t>
+          <t>49,72; 90,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 65,43</t>
+          <t>8,14; 65,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,32; 92,15</t>
+          <t>54,81; 91,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,07; 79,94</t>
+          <t>43,19; 80,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,3; 84,44</t>
+          <t>46,35; 86,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,42; 87,89</t>
+          <t>36,52; 86,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,79; 97,78</t>
+          <t>63,61; 97,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,05; 77,62</t>
+          <t>47,25; 77,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 84,22</t>
+          <t>53,82; 84,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,32; 69,74</t>
+          <t>28,89; 69,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,34; 94,37</t>
+          <t>67,7; 93,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,41; 95,85</t>
+          <t>66,29; 95,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,81; 73,23</t>
+          <t>45,76; 73,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,66; 69,81</t>
+          <t>34,23; 69,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,95; 97,09</t>
+          <t>71,2; 97,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,6; 77,77</t>
+          <t>46,33; 77,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,77; 64,99</t>
+          <t>35,34; 65,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,36; 76,95</t>
+          <t>39,41; 75,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,08; 78,52</t>
+          <t>47,42; 78,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,43; 81,82</t>
+          <t>59,63; 81,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,52; 64,98</t>
+          <t>44,52; 65,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,63; 68,74</t>
+          <t>43,88; 70,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,18; 85,25</t>
+          <t>60,95; 85,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 67,28</t>
+          <t>15,32; 68,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,31; 73,53</t>
+          <t>38,21; 75,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 79,15</t>
+          <t>26,5; 81,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,97; 91,02</t>
+          <t>49,58; 90,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,56; 86,48</t>
+          <t>48,61; 86,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,92; 83,08</t>
+          <t>55,67; 83,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 69,69</t>
+          <t>19,8; 74,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,88; 86,96</t>
+          <t>49,48; 87,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,81; 76,1</t>
+          <t>42,98; 75,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,78; 75,01</t>
+          <t>53,34; 74,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,49; 69,4</t>
+          <t>32,01; 68,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,02; 84,78</t>
+          <t>57,5; 84,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,18; 75,68</t>
+          <t>43,34; 78,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,25; 87,4</t>
+          <t>54,94; 86,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,2; 93,87</t>
+          <t>46,05; 93,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,23; 79,86</t>
+          <t>36,06; 79,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,7; 85,19</t>
+          <t>55,44; 87,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,54; 75,92</t>
+          <t>45,91; 77,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,64; 75,98</t>
+          <t>28,94; 77,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,9; 73,88</t>
+          <t>40,08; 74,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,65; 78,04</t>
+          <t>54,46; 77,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,35; 77,76</t>
+          <t>53,5; 76,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48,3; 81,03</t>
+          <t>46,77; 80,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,97; 72,19</t>
+          <t>46,4; 71,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,79; 76,0</t>
+          <t>54,79; 75,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,49; 73,47</t>
+          <t>56,48; 72,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,48; 67,8</t>
+          <t>43,74; 66,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,19; 84,51</t>
+          <t>65,62; 84,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,46; 74,61</t>
+          <t>59,33; 75,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 69,06</t>
+          <t>53,37; 69,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,39; 69,25</t>
+          <t>46,18; 68,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,95; 79,88</t>
+          <t>58,71; 79,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,94; 73,37</t>
+          <t>60,06; 72,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,16; 69,18</t>
+          <t>57,1; 68,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,02; 63,87</t>
+          <t>48,12; 64,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,01; 78,91</t>
+          <t>65,01; 80,01</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3271; 8404</t>
+          <t>3277; 8375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7006; 12735</t>
+          <t>6993; 12692</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>620; 5345</t>
+          <t>665; 5314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6521; 11063</t>
+          <t>6580; 10955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6826; 12970</t>
+          <t>7006; 13109</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6831; 13636</t>
+          <t>7486; 13896</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3536; 8534</t>
+          <t>3546; 8437</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15266; 23400</t>
+          <t>15222; 23382</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12488; 20174</t>
+          <t>12280; 20083</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16684; 25445</t>
+          <t>16263; 25389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5420; 12469</t>
+          <t>5164; 12497</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24199; 33915</t>
+          <t>24328; 33532</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10580; 14402</t>
+          <t>9961; 14407</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12182; 20362</t>
+          <t>12725; 20468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6791; 13680</t>
+          <t>6708; 13666</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14941; 20738</t>
+          <t>15209; 20825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12902; 21531</t>
+          <t>12826; 21512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11309; 19987</t>
+          <t>10869; 20295</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8090; 15421</t>
+          <t>7897; 15196</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11950; 20364</t>
+          <t>12299; 20291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25811; 34949</t>
+          <t>25471; 34772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26658; 38051</t>
+          <t>26074; 38088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17688; 27247</t>
+          <t>17391; 27777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28933; 40317</t>
+          <t>28826; 40252</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1131; 5295</t>
+          <t>1206; 5402</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7564; 14150</t>
+          <t>7353; 14504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2503; 7130</t>
+          <t>2387; 7328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7540; 13206</t>
+          <t>7193; 13102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7462; 13289</t>
+          <t>7470; 13337</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14144; 21013</t>
+          <t>14081; 21232</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1718; 6320</t>
+          <t>1795; 6797</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10246; 18227</t>
+          <t>10370; 18262</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9947; 17683</t>
+          <t>9986; 17568</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23505; 33405</t>
+          <t>23755; 33136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5873; 12545</t>
+          <t>5787; 12351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20934; 30069</t>
+          <t>20394; 29979</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9303; 16692</t>
+          <t>9558; 17376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11673; 18466</t>
+          <t>11609; 18268</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5092; 9716</t>
+          <t>4767; 9704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5991; 12517</t>
+          <t>5651; 12425</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12374; 18925</t>
+          <t>12315; 19498</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11214; 20012</t>
+          <t>12101; 20505</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3491; 9596</t>
+          <t>3655; 9754</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11535; 20837</t>
+          <t>11305; 21070</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24193; 34547</t>
+          <t>24109; 34474</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25812; 36925</t>
+          <t>25405; 36441</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11098; 18620</t>
+          <t>10746; 18464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20608; 31675</t>
+          <t>20361; 31577</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29434; 41587</t>
+          <t>29982; 41303</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46455; 60424</t>
+          <t>46450; 59996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20490; 31947</t>
+          <t>20610; 31256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41428; 53707</t>
+          <t>41701; 53764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47642; 60804</t>
+          <t>48345; 61351</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51812; 68059</t>
+          <t>52596; 68499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22837; 35626</t>
+          <t>23760; 35233</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58373; 79100</t>
+          <t>58136; 79103</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81647; 99940</t>
+          <t>81807; 99351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103352; 125068</t>
+          <t>103227; 124300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47336; 62952</t>
+          <t>47433; 63783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105685; 128287</t>
+          <t>105698; 130081</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>85,56%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>63,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>74,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,3%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,55; 85,77</t>
+          <t>41,85; 80,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,72; 90,24</t>
+          <t>45,63; 86,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 65,05</t>
+          <t>35,92; 86,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,81; 91,24</t>
+          <t>63,6; 97,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,19; 80,8</t>
+          <t>34,3; 86,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,35; 86,05</t>
+          <t>51,6; 90,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,52; 86,9</t>
+          <t>8,66; 67,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,61; 97,7</t>
+          <t>54,18; 92,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,25; 77,27</t>
+          <t>46,84; 77,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53,82; 84,03</t>
+          <t>53,21; 82,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,89; 69,9</t>
+          <t>32,39; 70,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,7; 93,31</t>
+          <t>70,27; 93,89</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>61,92%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>87,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>60,13%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>52,91%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,29; 95,88</t>
+          <t>48,26; 77,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,76; 73,61</t>
+          <t>36,04; 64,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 69,74</t>
+          <t>39,83; 75,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,2; 97,49</t>
+          <t>43,44; 77,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,33; 77,7</t>
+          <t>70,39; 95,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,34; 65,99</t>
+          <t>46,11; 73,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 75,82</t>
+          <t>35,79; 71,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,42; 78,24</t>
+          <t>63,3; 93,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,63; 81,41</t>
+          <t>58,95; 81,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,52; 65,04</t>
+          <t>43,43; 64,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,88; 70,08</t>
+          <t>43,24; 69,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,95; 85,11</t>
+          <t>56,98; 80,57</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70,11%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>56,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>53,73%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,48%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 68,65</t>
+          <t>49,41; 86,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,21; 75,37</t>
+          <t>54,58; 83,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 81,35</t>
+          <t>19,4; 74,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,58; 90,3</t>
+          <t>53,13; 89,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,61; 86,8</t>
+          <t>14,13; 68,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,67; 83,94</t>
+          <t>39,19; 74,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,8; 74,95</t>
+          <t>28,97; 77,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 87,13</t>
+          <t>50,54; 90,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,98; 75,61</t>
+          <t>42,81; 74,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,34; 74,4</t>
+          <t>53,24; 75,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,01; 68,33</t>
+          <t>32,48; 68,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,5; 84,52</t>
+          <t>59,41; 85,0</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>60,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>72,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>79,14%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,34; 78,78</t>
+          <t>54,69; 85,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,94; 86,47</t>
+          <t>45,0; 78,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,05; 93,76</t>
+          <t>31,81; 77,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,06; 79,28</t>
+          <t>43,89; 76,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,44; 87,77</t>
+          <t>42,63; 77,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,91; 77,79</t>
+          <t>54,47; 86,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 77,24</t>
+          <t>50,91; 93,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,08; 74,71</t>
+          <t>37,64; 80,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,46; 77,87</t>
+          <t>54,98; 78,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,5; 76,74</t>
+          <t>53,88; 76,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,77; 80,36</t>
+          <t>47,27; 81,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,4; 71,97</t>
+          <t>47,12; 72,24</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,79; 75,48</t>
+          <t>58,47; 75,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,48; 72,95</t>
+          <t>54,12; 70,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 66,33</t>
+          <t>45,52; 68,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,62; 84,6</t>
+          <t>60,48; 79,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,33; 75,29</t>
+          <t>54,32; 74,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,37; 69,5</t>
+          <t>55,68; 73,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,18; 68,48</t>
+          <t>42,92; 66,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,71; 79,88</t>
+          <t>63,28; 81,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,94</t>
+          <t>60,18; 73,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,1; 68,75</t>
+          <t>56,92; 68,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,12; 64,71</t>
+          <t>47,09; 63,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,01; 80,01</t>
+          <t>64,01; 78,34</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6340</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17653</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6189</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10533</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2616</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9365</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10307</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6340</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29787</t>
+          <t>27433</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3277; 8375</t>
+          <t>6789; 13030</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6993; 12692</t>
+          <t>7369; 13904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>665; 5314</t>
+          <t>3487; 8429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6580; 10955</t>
+          <t>13123; 20161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7006; 13109</t>
+          <t>3350; 8419</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7486; 13896</t>
+          <t>7258; 12726</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3546; 8437</t>
+          <t>707; 5547</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15222; 23382</t>
+          <t>6778; 11557</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12280; 20083</t>
+          <t>12172; 20045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16263; 25389</t>
+          <t>16077; 24998</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5164; 12497</t>
+          <t>5791; 12655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24328; 33532</t>
+          <t>23291; 31118</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17538</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14432</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16719</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10368</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18519</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17538</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15703</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11853</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>27667</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9961; 14407</t>
+          <t>13362; 21536</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12725; 20468</t>
+          <t>11084; 19971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6708; 13666</t>
+          <t>7983; 15208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15209; 20825</t>
+          <t>10125; 18127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12826; 21512</t>
+          <t>10577; 14417</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10869; 20295</t>
+          <t>12821; 20449</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7897; 15196</t>
+          <t>7014; 14044</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12299; 20291</t>
+          <t>10220; 15160</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25471; 34772</t>
+          <t>25181; 34682</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26074; 38088</t>
+          <t>25435; 37866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17391; 27777</t>
+          <t>17141; 27463</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28826; 40252</t>
+          <t>22480; 31789</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10774</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17867</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14762</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3058</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>10912</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4840</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10814</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10774</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17867</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25752</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1206; 5402</t>
+          <t>7593; 13323</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7353; 14504</t>
+          <t>13804; 21107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2387; 7328</t>
+          <t>1759; 6789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7193; 13102</t>
+          <t>10550; 17750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7470; 13337</t>
+          <t>1112; 5376</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14081; 21232</t>
+          <t>7541; 14330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1795; 6797</t>
+          <t>2610; 7012</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10370; 18262</t>
+          <t>7460; 13405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9986; 17568</t>
+          <t>9946; 17231</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23755; 33136</t>
+          <t>23711; 33714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5787; 12351</t>
+          <t>5871; 12324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20394; 29979</t>
+          <t>20566; 29422</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16175</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6912</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15394</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13394</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15384</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8191</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9427</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16290</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6912</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>24528</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9558; 17376</t>
+          <t>12150; 18939</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11609; 18268</t>
+          <t>11861; 20592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4767; 9704</t>
+          <t>4018; 9824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5651; 12425</t>
+          <t>11004; 19257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12315; 19498</t>
+          <t>9402; 17083</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12101; 20505</t>
+          <t>11508; 18319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3655; 9754</t>
+          <t>5269; 9704</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11305; 21070</t>
+          <t>5897; 12653</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24109; 34474</t>
+          <t>24339; 34822</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25405; 36441</t>
+          <t>25585; 36342</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10746; 18464</t>
+          <t>10861; 18634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20361; 31577</t>
+          <t>19196; 29428</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29982; 41303</t>
+          <t>47648; 61161</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46450; 59996</t>
+          <t>53340; 69245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20610; 31256</t>
+          <t>23419; 35223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41701; 53764</t>
+          <t>53751; 70273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48345; 61351</t>
+          <t>29720; 40835</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52596; 68499</t>
+          <t>45792; 60211</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23760; 35233</t>
+          <t>20224; 31287</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58136; 79103</t>
+          <t>37389; 48108</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81807; 99351</t>
+          <t>81973; 100480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103227; 124300</t>
+          <t>102905; 124602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47433; 63783</t>
+          <t>46415; 62759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105698; 130081</t>
+          <t>94707; 115901</t>
         </is>
       </c>
     </row>
